--- a/Assets/StreamingAssets/Dialog.xlsx
+++ b/Assets/StreamingAssets/Dialog.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\GitHub\six\Assets\StreamingAssets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE991FD9-4CCE-4C18-8FD6-752269704DF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55D5EDBB-6A03-4F3A-9F8B-E7866D305417}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="345" yWindow="855" windowWidth="15795" windowHeight="14490" firstSheet="43" activeTab="46" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="345" yWindow="855" windowWidth="15795" windowHeight="14490" firstSheet="44" activeTab="48" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="開場對話" sheetId="1" r:id="rId1"/>
@@ -61,13 +61,14 @@
     <sheet name="金平糖" sheetId="36" r:id="rId46"/>
     <sheet name="TRUE" sheetId="49" r:id="rId47"/>
     <sheet name="BAD" sheetId="50" r:id="rId48"/>
+    <sheet name="追逐" sheetId="55" r:id="rId49"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1036" uniqueCount="357">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1057" uniqueCount="362">
   <si>
     <t>對話內容</t>
   </si>
@@ -1658,6 +1659,26 @@
   </si>
   <si>
     <t>5-1-30-2.mp3</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>怎麼回事....</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>....璐璐!?</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>按下Shift可奔跑 請使用Shift逃離“怪物”的魔爪 並在“循環之室找到出口”</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>()^&amp;#$%*^$*</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>怪物.png</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -7191,6 +7212,105 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet49.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F5898AB-C152-4B2B-8EF0-D60050EC1BC9}">
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
+  <cols>
+    <col min="3" max="3" width="74" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C2" t="s">
+        <v>358</v>
+      </c>
+      <c r="D2" t="s">
+        <v>109</v>
+      </c>
+      <c r="F2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C3" t="s">
+        <v>357</v>
+      </c>
+      <c r="D3" t="s">
+        <v>109</v>
+      </c>
+      <c r="F3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>360</v>
+      </c>
+      <c r="C4" t="s">
+        <v>60</v>
+      </c>
+      <c r="D4" t="s">
+        <v>361</v>
+      </c>
+      <c r="F4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="C5" t="s">
+        <v>359</v>
+      </c>
+      <c r="D5" t="s">
+        <v>21</v>
+      </c>
+      <c r="F5" t="s">
+        <v>21</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="18" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{431C17E7-5C7D-4476-9C45-C86A2516A2EF}">
   <dimension ref="A1:F4"/>

--- a/Assets/StreamingAssets/Dialog.xlsx
+++ b/Assets/StreamingAssets/Dialog.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\GitHub\six\Assets\StreamingAssets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55D5EDBB-6A03-4F3A-9F8B-E7866D305417}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DB8022F-FF70-4690-B9F1-91C047BC7884}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="345" yWindow="855" windowWidth="15795" windowHeight="14490" firstSheet="44" activeTab="48" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="345" yWindow="855" windowWidth="15795" windowHeight="14490" firstSheet="45" activeTab="50" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="開場對話" sheetId="1" r:id="rId1"/>
@@ -62,13 +62,15 @@
     <sheet name="TRUE" sheetId="49" r:id="rId47"/>
     <sheet name="BAD" sheetId="50" r:id="rId48"/>
     <sheet name="追逐" sheetId="55" r:id="rId49"/>
+    <sheet name="妹妹房返回" sheetId="56" r:id="rId50"/>
+    <sheet name="離開追逐" sheetId="57" r:id="rId51"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1057" uniqueCount="362">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1077" uniqueCount="365">
   <si>
     <t>對話內容</t>
   </si>
@@ -1679,6 +1681,18 @@
   </si>
   <si>
     <t>怪物.png</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>好奇怪，暫時先別進去了</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>剛剛那到底是甚麼....</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>璐璐...?</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -7407,6 +7421,113 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet50.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{90C8F3F1-E371-493E-82CF-918CFCC0EAB6}">
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
+  <cols>
+    <col min="3" max="3" width="25" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="C2" t="s">
+        <v>362</v>
+      </c>
+      <c r="F2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="18" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet51.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C90788A9-A50A-4808-B0DA-6FABFFA5D3B9}">
+  <dimension ref="A1:F3"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
+  <cols>
+    <col min="3" max="3" width="19.375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C2" t="s">
+        <v>363</v>
+      </c>
+      <c r="F2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C3" t="s">
+        <v>364</v>
+      </c>
+      <c r="F3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="18" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B21B71F8-5C66-4198-8486-4D7386CC4E20}">
   <dimension ref="A1:F3"/>

--- a/Assets/StreamingAssets/Dialog.xlsx
+++ b/Assets/StreamingAssets/Dialog.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\GitHub\six\Assets\StreamingAssets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DB8022F-FF70-4690-B9F1-91C047BC7884}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12A2792D-0374-40F1-91B0-A9DE8B30CDAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="345" yWindow="855" windowWidth="15795" windowHeight="14490" firstSheet="45" activeTab="50" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="345" yWindow="855" windowWidth="15795" windowHeight="14490" firstSheet="46" activeTab="51" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="開場對話" sheetId="1" r:id="rId1"/>
@@ -64,13 +64,14 @@
     <sheet name="追逐" sheetId="55" r:id="rId49"/>
     <sheet name="妹妹房返回" sheetId="56" r:id="rId50"/>
     <sheet name="離開追逐" sheetId="57" r:id="rId51"/>
+    <sheet name="BE" sheetId="58" r:id="rId52"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1077" uniqueCount="365">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1089" uniqueCount="367">
   <si>
     <t>對話內容</t>
   </si>
@@ -1664,10 +1665,6 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>怎麼回事....</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>....璐璐!?</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -1693,6 +1690,18 @@
   </si>
   <si>
     <t>璐璐...?</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>BE_1.png</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>BAD END-永遠的玩伴</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>怎麼回事....先離開再說吧!</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -7262,7 +7271,7 @@
         <v>24</v>
       </c>
       <c r="C2" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="D2" t="s">
         <v>109</v>
@@ -7279,7 +7288,7 @@
         <v>24</v>
       </c>
       <c r="C3" t="s">
-        <v>357</v>
+        <v>366</v>
       </c>
       <c r="D3" t="s">
         <v>109</v>
@@ -7293,13 +7302,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C4" t="s">
         <v>60</v>
       </c>
       <c r="D4" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="F4" t="s">
         <v>21</v>
@@ -7310,7 +7319,7 @@
         <v>4</v>
       </c>
       <c r="C5" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="D5" t="s">
         <v>21</v>
@@ -7454,7 +7463,10 @@
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>362</v>
+        <v>361</v>
+      </c>
+      <c r="D2" t="s">
+        <v>21</v>
       </c>
       <c r="F2" t="s">
         <v>21</v>
@@ -7502,7 +7514,10 @@
         <v>24</v>
       </c>
       <c r="C2" t="s">
-        <v>363</v>
+        <v>362</v>
+      </c>
+      <c r="D2" t="s">
+        <v>109</v>
       </c>
       <c r="F2" t="s">
         <v>21</v>
@@ -7516,10 +7531,61 @@
         <v>24</v>
       </c>
       <c r="C3" t="s">
+        <v>363</v>
+      </c>
+      <c r="D3" t="s">
+        <v>109</v>
+      </c>
+      <c r="F3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="18" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet52.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F76E551-BFD4-4933-B5EC-8402039646A0}">
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
+  <cols>
+    <col min="3" max="3" width="21.625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="C2" t="s">
+        <v>365</v>
+      </c>
+      <c r="D2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F2" t="s">
         <v>364</v>
-      </c>
-      <c r="F3" t="s">
-        <v>21</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/StreamingAssets/Dialog.xlsx
+++ b/Assets/StreamingAssets/Dialog.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\GitHub\six\Assets\StreamingAssets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12A2792D-0374-40F1-91B0-A9DE8B30CDAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B806F4A2-553E-4DB4-B096-78CB0E9577C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="345" yWindow="855" windowWidth="15795" windowHeight="14490" firstSheet="46" activeTab="51" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="13005" yWindow="990" windowWidth="15795" windowHeight="14490" firstSheet="48" activeTab="52" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="開場對話" sheetId="1" r:id="rId1"/>
@@ -64,14 +64,16 @@
     <sheet name="追逐" sheetId="55" r:id="rId49"/>
     <sheet name="妹妹房返回" sheetId="56" r:id="rId50"/>
     <sheet name="離開追逐" sheetId="57" r:id="rId51"/>
-    <sheet name="BE" sheetId="58" r:id="rId52"/>
+    <sheet name="出妹妹房間" sheetId="60" r:id="rId52"/>
+    <sheet name="TRUE糖返回" sheetId="59" r:id="rId53"/>
+    <sheet name="BE" sheetId="58" r:id="rId54"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1089" uniqueCount="367">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1121" uniqueCount="372">
   <si>
     <t>對話內容</t>
   </si>
@@ -1681,10 +1683,6 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>好奇怪，暫時先別進去了</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>剛剛那到底是甚麼....</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -1702,6 +1700,30 @@
   </si>
   <si>
     <t>怎麼回事....先離開再說吧!</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>暫時先不用進去了</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>姐姐!</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>謝謝妳!最喜歡姊姊了!</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>....嗯</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>(感覺....暖暖的)</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>閉眼微笑.png</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -7288,7 +7310,7 @@
         <v>24</v>
       </c>
       <c r="C3" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="D3" t="s">
         <v>109</v>
@@ -7463,7 +7485,7 @@
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="D2" t="s">
         <v>21</v>
@@ -7514,7 +7536,7 @@
         <v>24</v>
       </c>
       <c r="C2" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="D2" t="s">
         <v>109</v>
@@ -7531,7 +7553,7 @@
         <v>24</v>
       </c>
       <c r="C3" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="D3" t="s">
         <v>109</v>
@@ -7547,6 +7569,156 @@
 </file>
 
 <file path=xl/worksheets/sheet52.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B579BE0A-465E-4B84-9BF6-85B30187D89C}">
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
+  <cols>
+    <col min="3" max="3" width="21.875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>121</v>
+      </c>
+      <c r="C2" t="s">
+        <v>367</v>
+      </c>
+      <c r="D2" t="s">
+        <v>130</v>
+      </c>
+      <c r="F2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C3" t="s">
+        <v>168</v>
+      </c>
+      <c r="D3" t="s">
+        <v>61</v>
+      </c>
+      <c r="F3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>121</v>
+      </c>
+      <c r="C4" t="s">
+        <v>368</v>
+      </c>
+      <c r="D4" t="s">
+        <v>266</v>
+      </c>
+      <c r="F4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5" t="s">
+        <v>369</v>
+      </c>
+      <c r="D5" t="s">
+        <v>29</v>
+      </c>
+      <c r="F5" t="s">
+        <v>21</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="18" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet53.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DFCC438D-A915-4C77-A296-459DDF53F0B6}">
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C2" t="s">
+        <v>370</v>
+      </c>
+      <c r="D2" t="s">
+        <v>371</v>
+      </c>
+      <c r="F2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="18" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet54.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F76E551-BFD4-4933-B5EC-8402039646A0}">
   <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
@@ -7579,13 +7751,13 @@
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="D2" t="s">
         <v>21</v>
       </c>
       <c r="F2" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
   </sheetData>
